--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,48 +904,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135039486</v>
+        <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>92043</v>
+        <v>79580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647936</v>
+        <v>648079</v>
       </c>
       <c r="R4" t="n">
-        <v>6944664</v>
+        <v>6944275</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Huvudsakligen 3-4 meter upp i en senvuxen gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +994,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039486</t>
+          <t>https://artportalen.se/Sighting/137306302</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135039492</v>
+        <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>92043</v>
+        <v>79580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>637</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647729</v>
+        <v>648066</v>
       </c>
       <c r="R5" t="n">
-        <v>6944666</v>
+        <v>6944281</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1096,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039492</t>
+          <t>https://artportalen.se/Sighting/137306578</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1322966</v>
+        <v>135039486</v>
       </c>
       <c r="B6" t="n">
-        <v>93197</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,46 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647800</v>
+        <v>647936</v>
       </c>
       <c r="R6" t="n">
-        <v>6944135</v>
+        <v>6944664</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,12 +1178,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,45 +1204,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322966</t>
+          <t>https://artportalen.se/Sighting/135039486</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1322967</v>
+        <v>135039492</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,46 +1236,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647805</v>
+        <v>647729</v>
       </c>
       <c r="R7" t="n">
-        <v>6944182</v>
+        <v>6944666</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,12 +1290,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,45 +1316,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322967</t>
+          <t>https://artportalen.se/Sighting/135039492</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1322968</v>
+        <v>137302205</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,43 +1348,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647877</v>
+        <v>647947</v>
       </c>
       <c r="R8" t="n">
-        <v>6943956</v>
+        <v>6944551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,12 +1402,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,80 +1428,66 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322968</t>
+          <t>https://artportalen.se/Sighting/137302205</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135039487</v>
+        <v>137300719</v>
       </c>
       <c r="B9" t="n">
-        <v>92006</v>
+        <v>83381</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647939</v>
+        <v>647928</v>
       </c>
       <c r="R9" t="n">
-        <v>6944638</v>
+        <v>6944580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,22 +1514,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,27 +1544,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039487</t>
+          <t>https://artportalen.se/Sighting/137300719</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1763376</v>
+        <v>1322966</v>
       </c>
       <c r="B10" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,34 +1572,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>647855</v>
+        <v>647800</v>
       </c>
       <c r="R10" t="n">
-        <v>6944106</v>
+        <v>6944135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,6 +1652,16 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1715,62 +1680,63 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763376</t>
+          <t>https://artportalen.se/Sighting/1322966</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135039490</v>
+        <v>1322967</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>647904</v>
+        <v>647805</v>
       </c>
       <c r="R11" t="n">
-        <v>6944512</v>
+        <v>6944182</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,22 +1760,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,81 +1776,92 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039490</t>
+          <t>https://artportalen.se/Sighting/1322967</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135039491</v>
+        <v>1322968</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647833</v>
+        <v>647877</v>
       </c>
       <c r="R12" t="n">
-        <v>6944586</v>
+        <v>6943956</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,27 +1885,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Uppskrämda.</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,31 +1901,45 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039491</t>
+          <t>https://artportalen.se/Sighting/1322968</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135039489</v>
+        <v>137300025</v>
       </c>
       <c r="B13" t="n">
-        <v>58141</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,49 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647942</v>
+        <v>647897</v>
       </c>
       <c r="R13" t="n">
-        <v>6944520</v>
+        <v>6944605</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2047,22 +2001,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,27 +2031,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039489</t>
+          <t>https://artportalen.se/Sighting/137300025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1763373</v>
+        <v>137300385</v>
       </c>
       <c r="B14" t="n">
-        <v>93235</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,43 +2059,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>647086</v>
+        <v>647876</v>
       </c>
       <c r="R14" t="n">
-        <v>6943714</v>
+        <v>6944586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,12 +2113,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,31 +2143,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Matilda Sandgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Matilda Sandgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763373</t>
+          <t>https://artportalen.se/Sighting/137300385</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1322969</v>
+        <v>137302420</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,26 +2188,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>647718</v>
+        <v>647875</v>
       </c>
       <c r="R15" t="n">
-        <v>6943739</v>
+        <v>6944553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2283,12 +2225,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,45 +2251,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322969</t>
+          <t>https://artportalen.se/Sighting/137302420</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1763375</v>
+        <v>137307953</v>
       </c>
       <c r="B16" t="n">
-        <v>93235</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,46 +2283,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>647646</v>
+        <v>647873</v>
       </c>
       <c r="R16" t="n">
-        <v>6943850</v>
+        <v>6944550</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2408,12 +2337,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,40 +2363,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763375</t>
+          <t>https://artportalen.se/Sighting/137307953</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>210541</v>
+        <v>137308684</v>
       </c>
       <c r="B17" t="n">
-        <v>92208</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,46 +2395,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slätberget, Fälleberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>647886</v>
+        <v>647827</v>
       </c>
       <c r="R17" t="n">
-        <v>6943600</v>
+        <v>6944603</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2528,12 +2449,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,41 +2475,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>svacka i hällmarkstallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/210541</t>
+          <t>https://artportalen.se/Sighting/137308684</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>429255</v>
+        <v>137310231</v>
       </c>
       <c r="B18" t="n">
-        <v>91909</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2586,43 +2507,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slätberget, Fälleberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>647886</v>
+        <v>647868</v>
       </c>
       <c r="R18" t="n">
-        <v>6943600</v>
+        <v>6944589</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2649,12 +2561,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2665,88 +2577,72 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>svacka i hällmarkstallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/429255</t>
+          <t>https://artportalen.se/Sighting/137310231</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1323584</v>
+        <v>137308688</v>
       </c>
       <c r="B19" t="n">
-        <v>93197</v>
+        <v>92142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>647794</v>
+        <v>647928</v>
       </c>
       <c r="R19" t="n">
-        <v>6943662</v>
+        <v>6944362</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2770,12 +2666,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,91 +2690,84 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323584</t>
+          <t>https://artportalen.se/Sighting/137308688</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1322963</v>
+        <v>135039487</v>
       </c>
       <c r="B20" t="n">
-        <v>93197</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>647228</v>
+        <v>647939</v>
       </c>
       <c r="R20" t="n">
-        <v>6943441</v>
+        <v>6944638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2895,12 +2794,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,89 +2820,66 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322963</t>
+          <t>https://artportalen.se/Sighting/135039487</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1322964</v>
+        <v>137300276</v>
       </c>
       <c r="B21" t="n">
-        <v>93197</v>
+        <v>92121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>647213</v>
+        <v>647918</v>
       </c>
       <c r="R21" t="n">
-        <v>6943460</v>
+        <v>6944595</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3020,12 +2906,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,89 +2932,66 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322964</t>
+          <t>https://artportalen.se/Sighting/137300276</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1763369</v>
+        <v>137301616</v>
       </c>
       <c r="B22" t="n">
-        <v>93235</v>
+        <v>92121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>647228</v>
+        <v>647899</v>
       </c>
       <c r="R22" t="n">
-        <v>6943441</v>
+        <v>6944515</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3145,12 +3018,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3161,89 +3034,66 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763369</t>
+          <t>https://artportalen.se/Sighting/137301616</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1763370</v>
+        <v>137303303</v>
       </c>
       <c r="B23" t="n">
-        <v>93235</v>
+        <v>92121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>647213</v>
+        <v>647859</v>
       </c>
       <c r="R23" t="n">
-        <v>6943460</v>
+        <v>6944480</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3270,12 +3120,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3286,34 +3146,4414 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137303303</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1763376</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>647855</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6944106</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Hans Sundström</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Hans Sundström</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Steget Före</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763376</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137299812</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>647851</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6944635</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137299812</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137299866</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>647898</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6944618</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137299866</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137302563</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>647861</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6944549</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137302563</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137303975</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>648276</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6944192</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137303975</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137304833</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>648139</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6944148</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137304833</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137305557</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>648000</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6944074</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305557</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137305982</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>648060</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6944250</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305982</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137306841</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>647990</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6944630</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137306841</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137307957</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>647990</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6944629</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307957</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137310228</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>647865</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6944615</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137310228</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137310230</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>647879</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6944648</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137310230</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137302387</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79513</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>647890</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6944461</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137302387</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137307952</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79537</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>647859</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6944610</v>
+      </c>
+      <c r="S37" t="n">
+        <v>14</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307952</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137307954</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79537</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>647884</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6944388</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307954</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137308685</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79537</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>647831</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6944609</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137308685</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137310227</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79537</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>647878</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6944660</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137310227</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137307956</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>647938</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6944333</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137307956</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137308686</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>647835</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6944599</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137308686</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137308687</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>647911</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6944464</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137308687</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135039490</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>647904</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6944512</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039490</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135039491</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>647833</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6944586</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Uppskrämda.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039491</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137299948</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57220</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>647834</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6944597</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137299948</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137303210</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57220</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>647860</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6944223</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Natträd</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137303210</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135039489</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>1, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>647942</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6944520</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039489</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137302329</v>
+      </c>
+      <c r="B49" t="n">
+        <v>111398</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>647885</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6944478</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137302329</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137301096</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99404</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>647887</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6944485</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137301096</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137303092</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92549</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>647853</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6944493</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137303092</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1763373</v>
+      </c>
+      <c r="B52" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>647086</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6943714</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763373</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1322969</v>
+      </c>
+      <c r="B53" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>647718</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6943739</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322969</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1763375</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>647646</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6943850</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763375</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>210541</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>658</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Slätberget, Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>647886</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6943600</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>svacka i hällmarkstallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/210541</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>429255</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Slätberget, Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>647886</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6943600</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>svacka i hällmarkstallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429255</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1323584</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>647794</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6943662</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1323584</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1322963</v>
+      </c>
+      <c r="B58" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>647228</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6943441</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322963</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1322964</v>
+      </c>
+      <c r="B59" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>647213</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322964</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1763369</v>
+      </c>
+      <c r="B60" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>647228</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6943441</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763369</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1763370</v>
+      </c>
+      <c r="B61" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>647213</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1763370</t>
         </is>
@@ -3343,6 +7583,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ61"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,48 +1113,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135039486</v>
+        <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>92043</v>
+        <v>79580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>637</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647936</v>
+        <v>648050</v>
       </c>
       <c r="R6" t="n">
-        <v>6944664</v>
+        <v>6944266</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,65 +1198,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039486</t>
+          <t>https://artportalen.se/Sighting/137324302</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135039492</v>
+        <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>92043</v>
+        <v>79580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>637</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647729</v>
+        <v>648045</v>
       </c>
       <c r="R7" t="n">
-        <v>6944666</v>
+        <v>6944279</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,22 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,49 +1300,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039492</t>
+          <t>https://artportalen.se/Sighting/137324637</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137302205</v>
+        <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>79580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647947</v>
+        <v>648033</v>
       </c>
       <c r="R8" t="n">
-        <v>6944551</v>
+        <v>6944317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,22 +1382,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,27 +1407,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302205</t>
+          <t>https://artportalen.se/Sighting/137325198</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137300719</v>
+        <v>135039486</v>
       </c>
       <c r="B9" t="n">
-        <v>83381</v>
+        <v>92043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,37 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647928</v>
+        <v>647936</v>
       </c>
       <c r="R9" t="n">
-        <v>6944580</v>
+        <v>6944664</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,27 +1519,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300719</t>
+          <t>https://artportalen.se/Sighting/135039486</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1322966</v>
+        <v>135039492</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,46 +1547,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>647800</v>
+        <v>647729</v>
       </c>
       <c r="R10" t="n">
-        <v>6944135</v>
+        <v>6944666</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,12 +1601,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,45 +1627,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322966</t>
+          <t>https://artportalen.se/Sighting/135039492</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1322967</v>
+        <v>137302205</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>92159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,43 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>647805</v>
+        <v>647947</v>
       </c>
       <c r="R11" t="n">
-        <v>6944182</v>
+        <v>6944551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,12 +1713,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,45 +1739,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322967</t>
+          <t>https://artportalen.se/Sighting/137302205</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1322968</v>
+        <v>137300719</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>83381</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,43 +1771,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647877</v>
+        <v>647928</v>
       </c>
       <c r="R12" t="n">
-        <v>6943956</v>
+        <v>6944580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,12 +1825,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,45 +1851,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322968</t>
+          <t>https://artportalen.se/Sighting/137300719</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137300025</v>
+        <v>1322966</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,17 +1900,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647897</v>
+        <v>647800</v>
       </c>
       <c r="R13" t="n">
-        <v>6944605</v>
+        <v>6944135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,22 +1946,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,31 +1962,45 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300025</t>
+          <t>https://artportalen.se/Sighting/1322966</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137300385</v>
+        <v>1322967</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,17 +2025,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>647876</v>
+        <v>647805</v>
       </c>
       <c r="R14" t="n">
-        <v>6944586</v>
+        <v>6944182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,22 +2071,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,31 +2087,45 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Matilda Sandgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Matilda Sandgren</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300385</t>
+          <t>https://artportalen.se/Sighting/1322967</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137302420</v>
+        <v>1322968</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,17 +2150,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>647875</v>
+        <v>647877</v>
       </c>
       <c r="R15" t="n">
-        <v>6944553</v>
+        <v>6943956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,22 +2196,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,31 +2212,45 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302420</t>
+          <t>https://artportalen.se/Sighting/1322968</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137307953</v>
+        <v>137300025</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,17 +2278,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>647873</v>
+        <v>647897</v>
       </c>
       <c r="R16" t="n">
-        <v>6944550</v>
+        <v>6944605</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,27 +2342,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307953</t>
+          <t>https://artportalen.se/Sighting/137300025</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137308684</v>
+        <v>137300385</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,17 +2390,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>647827</v>
+        <v>647876</v>
       </c>
       <c r="R17" t="n">
-        <v>6944603</v>
+        <v>6944586</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2454,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2439,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,27 +2454,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Matilda Sandgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Matilda Sandgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308684</t>
+          <t>https://artportalen.se/Sighting/137300385</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137310231</v>
+        <v>137302420</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,17 +2502,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>647868</v>
+        <v>647875</v>
       </c>
       <c r="R18" t="n">
-        <v>6944589</v>
+        <v>6944553</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,9 +2539,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,68 +2566,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310231</t>
+          <t>https://artportalen.se/Sighting/137302420</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137308688</v>
+        <v>137307953</v>
       </c>
       <c r="B19" t="n">
-        <v>92142</v>
+        <v>93456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>647928</v>
+        <v>647873</v>
       </c>
       <c r="R19" t="n">
-        <v>6944362</v>
+        <v>6944550</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2671,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2663,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,87 +2672,71 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308688</t>
+          <t>https://artportalen.se/Sighting/137307953</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135039487</v>
+        <v>137308684</v>
       </c>
       <c r="B20" t="n">
-        <v>92006</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>647939</v>
+        <v>647827</v>
       </c>
       <c r="R20" t="n">
-        <v>6944638</v>
+        <v>6944603</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2794,22 +2760,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2824,65 +2790,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039487</t>
+          <t>https://artportalen.se/Sighting/137308684</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137300276</v>
+        <v>137310231</v>
       </c>
       <c r="B21" t="n">
-        <v>92121</v>
+        <v>93456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>647918</v>
+        <v>647868</v>
       </c>
       <c r="R21" t="n">
-        <v>6944595</v>
+        <v>6944589</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2909,19 +2875,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,62 +2892,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300276</t>
+          <t>https://artportalen.se/Sighting/137310231</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137301616</v>
+        <v>137319904</v>
       </c>
       <c r="B22" t="n">
-        <v>92121</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>647899</v>
+        <v>647797</v>
       </c>
       <c r="R22" t="n">
-        <v>6944515</v>
+        <v>6944578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,12 +2974,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3049,38 +3005,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137301616</t>
+          <t>https://artportalen.se/Sighting/137319904</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137303303</v>
+        <v>137326956</v>
       </c>
       <c r="B23" t="n">
-        <v>92121</v>
+        <v>93456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3090,10 +3046,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>647859</v>
+        <v>648123</v>
       </c>
       <c r="R23" t="n">
-        <v>6944480</v>
+        <v>6944279</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,22 +3076,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,65 +3096,68 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303303</t>
+          <t>https://artportalen.se/Sighting/137326956</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1763376</v>
+        <v>137308688</v>
       </c>
       <c r="B24" t="n">
-        <v>93235</v>
+        <v>92143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4660</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>647855</v>
+        <v>647928</v>
       </c>
       <c r="R24" t="n">
-        <v>6944106</v>
+        <v>6944362</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,12 +3181,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,84 +3205,87 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763376</t>
+          <t>https://artportalen.se/Sighting/137308688</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137299812</v>
+        <v>135039487</v>
       </c>
       <c r="B25" t="n">
-        <v>93493</v>
+        <v>92006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>647851</v>
+        <v>647939</v>
       </c>
       <c r="R25" t="n">
-        <v>6944635</v>
+        <v>6944638</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3347,22 +3309,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,49 +3339,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137299812</t>
+          <t>https://artportalen.se/Sighting/135039487</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137299866</v>
+        <v>137300276</v>
       </c>
       <c r="B26" t="n">
-        <v>93493</v>
+        <v>92122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3429,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>647898</v>
+        <v>647918</v>
       </c>
       <c r="R26" t="n">
-        <v>6944618</v>
+        <v>6944595</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3464,7 +3426,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3474,7 +3436,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,38 +3462,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137299866</t>
+          <t>https://artportalen.se/Sighting/137300276</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137302563</v>
+        <v>137301616</v>
       </c>
       <c r="B27" t="n">
-        <v>93493</v>
+        <v>92122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3541,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>647861</v>
+        <v>647899</v>
       </c>
       <c r="R27" t="n">
-        <v>6944549</v>
+        <v>6944515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,19 +3536,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,65 +3553,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302563</t>
+          <t>https://artportalen.se/Sighting/137301616</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137303975</v>
+        <v>137303303</v>
       </c>
       <c r="B28" t="n">
-        <v>93493</v>
+        <v>92122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>648276</v>
+        <v>647859</v>
       </c>
       <c r="R28" t="n">
-        <v>6944192</v>
+        <v>6944480</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3688,7 +3640,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3698,7 +3650,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,49 +3665,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303975</t>
+          <t>https://artportalen.se/Sighting/137303303</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137304833</v>
+        <v>137322516</v>
       </c>
       <c r="B29" t="n">
-        <v>93493</v>
+        <v>92122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3765,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>648139</v>
+        <v>647644</v>
       </c>
       <c r="R29" t="n">
-        <v>6944148</v>
+        <v>6944201</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,12 +3747,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,16 +3778,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137304833</t>
+          <t>https://artportalen.se/Sighting/137322516</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137305557</v>
+        <v>1763376</v>
       </c>
       <c r="B30" t="n">
-        <v>93493</v>
+        <v>93235</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,14 +3815,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648000</v>
+        <v>647855</v>
       </c>
       <c r="R30" t="n">
-        <v>6944074</v>
+        <v>6944106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,12 +3849,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3917,27 +3869,31 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305557</t>
+          <t>https://artportalen.se/Sighting/1763376</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137305982</v>
+        <v>137299812</v>
       </c>
       <c r="B31" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,20 +3918,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648060</v>
+        <v>647851</v>
       </c>
       <c r="R31" t="n">
-        <v>6944250</v>
+        <v>6944635</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4002,9 +3967,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4019,27 +3994,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305982</t>
+          <t>https://artportalen.se/Sighting/137299812</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137306841</v>
+        <v>137299866</v>
       </c>
       <c r="B32" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,10 +4046,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>647990</v>
+        <v>647898</v>
       </c>
       <c r="R32" t="n">
-        <v>6944630</v>
+        <v>6944618</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4104,9 +4079,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,27 +4106,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137306841</t>
+          <t>https://artportalen.se/Sighting/137299866</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137307957</v>
+        <v>137302563</v>
       </c>
       <c r="B33" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,17 +4154,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>647990</v>
+        <v>647861</v>
       </c>
       <c r="R33" t="n">
-        <v>6944629</v>
+        <v>6944549</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,7 +4193,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4218,7 +4203,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4233,27 +4218,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307957</t>
+          <t>https://artportalen.se/Sighting/137302563</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137310228</v>
+        <v>137303975</v>
       </c>
       <c r="B34" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,13 +4270,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>647865</v>
+        <v>648276</v>
       </c>
       <c r="R34" t="n">
-        <v>6944615</v>
+        <v>6944192</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,9 +4303,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4335,27 +4330,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310228</t>
+          <t>https://artportalen.se/Sighting/137303975</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137310230</v>
+        <v>137304833</v>
       </c>
       <c r="B35" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,17 +4378,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>647879</v>
+        <v>648139</v>
       </c>
       <c r="R35" t="n">
-        <v>6944648</v>
+        <v>6944148</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4448,38 +4443,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310230</t>
+          <t>https://artportalen.se/Sighting/137304833</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137302387</v>
+        <v>137305557</v>
       </c>
       <c r="B36" t="n">
-        <v>79513</v>
+        <v>93494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4489,10 +4484,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>647890</v>
+        <v>648000</v>
       </c>
       <c r="R36" t="n">
-        <v>6944461</v>
+        <v>6944074</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,57 +4545,54 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302387</t>
+          <t>https://artportalen.se/Sighting/137305557</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137307952</v>
+        <v>137305982</v>
       </c>
       <c r="B37" t="n">
-        <v>79537</v>
+        <v>93494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>647859</v>
+        <v>648060</v>
       </c>
       <c r="R37" t="n">
-        <v>6944610</v>
+        <v>6944250</v>
       </c>
       <c r="S37" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4627,111 +4619,82 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307952</t>
+          <t>https://artportalen.se/Sighting/137305982</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137307954</v>
+        <v>137306841</v>
       </c>
       <c r="B38" t="n">
-        <v>79537</v>
+        <v>93494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>647884</v>
+        <v>647990</v>
       </c>
       <c r="R38" t="n">
-        <v>6944388</v>
+        <v>6944630</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4758,111 +4721,82 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307954</t>
+          <t>https://artportalen.se/Sighting/137306841</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137308685</v>
+        <v>137307957</v>
       </c>
       <c r="B39" t="n">
-        <v>79537</v>
+        <v>93494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>647831</v>
+        <v>647990</v>
       </c>
       <c r="R39" t="n">
-        <v>6944609</v>
+        <v>6944629</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4891,7 +4825,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4901,12 +4835,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4915,71 +4844,55 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308685</t>
+          <t>https://artportalen.se/Sighting/137307957</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137310227</v>
+        <v>137310228</v>
       </c>
       <c r="B40" t="n">
-        <v>79537</v>
+        <v>93494</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4989,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>647878</v>
+        <v>647865</v>
       </c>
       <c r="R40" t="n">
-        <v>6944660</v>
+        <v>6944615</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5050,58 +4963,54 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310227</t>
+          <t>https://artportalen.se/Sighting/137310228</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137307956</v>
+        <v>137310230</v>
       </c>
       <c r="B41" t="n">
-        <v>58030</v>
+        <v>93494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>647938</v>
+        <v>647879</v>
       </c>
       <c r="R41" t="n">
-        <v>6944333</v>
+        <v>6944648</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5128,19 +5037,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,27 +5054,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307956</t>
+          <t>https://artportalen.se/Sighting/137310230</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137308686</v>
+        <v>137323297</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>93494</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5183,41 +5082,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>647835</v>
+        <v>647851</v>
       </c>
       <c r="R42" t="n">
-        <v>6944599</v>
+        <v>6944063</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5241,27 +5136,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,27 +5156,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308686</t>
+          <t>https://artportalen.se/Sighting/137323297</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137308687</v>
+        <v>137325669</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>93494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5304,41 +5184,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>647911</v>
+        <v>647968</v>
       </c>
       <c r="R43" t="n">
-        <v>6944464</v>
+        <v>6944329</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5362,27 +5238,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:34</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5397,73 +5258,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308687</t>
+          <t>https://artportalen.se/Sighting/137325669</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135039490</v>
+        <v>137325868</v>
       </c>
       <c r="B44" t="n">
-        <v>57167</v>
+        <v>93494</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>647904</v>
+        <v>647955</v>
       </c>
       <c r="R44" t="n">
-        <v>6944512</v>
+        <v>6944342</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5487,22 +5340,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5517,77 +5360,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039490</t>
+          <t>https://artportalen.se/Sighting/137325868</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135039491</v>
+        <v>137327164</v>
       </c>
       <c r="B45" t="n">
-        <v>57167</v>
+        <v>93494</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>647833</v>
+        <v>648166</v>
       </c>
       <c r="R45" t="n">
-        <v>6944586</v>
+        <v>6944162</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5611,27 +5442,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Uppskrämda.</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5646,66 +5462,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039491</t>
+          <t>https://artportalen.se/Sighting/137327164</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137299948</v>
+        <v>137327225</v>
       </c>
       <c r="B46" t="n">
-        <v>57220</v>
+        <v>93494</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>647834</v>
+        <v>648189</v>
       </c>
       <c r="R46" t="n">
-        <v>6944597</v>
+        <v>6944175</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5729,22 +5544,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5759,66 +5564,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137299948</t>
+          <t>https://artportalen.se/Sighting/137327225</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137303210</v>
+        <v>137327248</v>
       </c>
       <c r="B47" t="n">
-        <v>57220</v>
+        <v>93494</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>647860</v>
+        <v>648188</v>
       </c>
       <c r="R47" t="n">
-        <v>6944223</v>
+        <v>6944181</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5842,27 +5646,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Natträd</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5877,27 +5666,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303210</t>
+          <t>https://artportalen.se/Sighting/137327248</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135039489</v>
+        <v>137327306</v>
       </c>
       <c r="B48" t="n">
-        <v>58141</v>
+        <v>93494</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5905,49 +5694,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>647942</v>
+        <v>648207</v>
       </c>
       <c r="R48" t="n">
-        <v>6944520</v>
+        <v>6944170</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5971,22 +5748,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,49 +5768,49 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039489</t>
+          <t>https://artportalen.se/Sighting/137327306</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137302329</v>
+        <v>137327400</v>
       </c>
       <c r="B49" t="n">
-        <v>111398</v>
+        <v>93494</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220240</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6053,10 +5820,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>647885</v>
+        <v>648304</v>
       </c>
       <c r="R49" t="n">
-        <v>6944478</v>
+        <v>6944246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6083,12 +5850,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,38 +5881,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302329</t>
+          <t>https://artportalen.se/Sighting/137327400</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137301096</v>
+        <v>137327418</v>
       </c>
       <c r="B50" t="n">
-        <v>99404</v>
+        <v>93494</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6155,10 +5922,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>647887</v>
+        <v>648306</v>
       </c>
       <c r="R50" t="n">
-        <v>6944485</v>
+        <v>6944280</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6185,12 +5952,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6216,38 +5983,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137301096</t>
+          <t>https://artportalen.se/Sighting/137327418</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137303092</v>
+        <v>137302387</v>
       </c>
       <c r="B51" t="n">
-        <v>92549</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6040162</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6257,10 +6024,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>647853</v>
+        <v>647890</v>
       </c>
       <c r="R51" t="n">
-        <v>6944493</v>
+        <v>6944461</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6290,19 +6057,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6317,71 +6074,62 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303092</t>
+          <t>https://artportalen.se/Sighting/137302387</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1763373</v>
+        <v>137319834</v>
       </c>
       <c r="B52" t="n">
-        <v>93235</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>647086</v>
+        <v>647807</v>
       </c>
       <c r="R52" t="n">
-        <v>6943714</v>
+        <v>6944577</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6408,12 +6156,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6428,75 +6176,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763373</t>
+          <t>https://artportalen.se/Sighting/137319834</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1322969</v>
+        <v>137326463</v>
       </c>
       <c r="B53" t="n">
-        <v>93197</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>647718</v>
+        <v>647966</v>
       </c>
       <c r="R53" t="n">
-        <v>6943739</v>
+        <v>6944439</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6523,12 +6258,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6539,92 +6274,72 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322969</t>
+          <t>https://artportalen.se/Sighting/137326463</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1763375</v>
+        <v>137307952</v>
       </c>
       <c r="B54" t="n">
-        <v>93235</v>
+        <v>79537</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>647646</v>
+        <v>647859</v>
       </c>
       <c r="R54" t="n">
-        <v>6943850</v>
+        <v>6944610</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6648,12 +6363,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6662,89 +6387,90 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763375</t>
+          <t>https://artportalen.se/Sighting/137307952</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>210541</v>
+        <v>137307954</v>
       </c>
       <c r="B55" t="n">
-        <v>92208</v>
+        <v>79537</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slätberget, Fälleberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>647886</v>
+        <v>647884</v>
       </c>
       <c r="R55" t="n">
-        <v>6943600</v>
+        <v>6944388</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6768,12 +6494,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6782,90 +6518,90 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>svacka i hällmarkstallnaturskog</t>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/210541</t>
+          <t>https://artportalen.se/Sighting/137307954</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>429255</v>
+        <v>137308685</v>
       </c>
       <c r="B56" t="n">
-        <v>91909</v>
+        <v>79537</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Slätberget, Fälleberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>647886</v>
+        <v>647831</v>
       </c>
       <c r="R56" t="n">
-        <v>6943600</v>
+        <v>6944609</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6889,12 +6625,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6903,90 +6654,87 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>svacka i hällmarkstallnaturskog</t>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/429255</t>
+          <t>https://artportalen.se/Sighting/137308685</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1323584</v>
+        <v>137310227</v>
       </c>
       <c r="B57" t="n">
-        <v>93197</v>
+        <v>79537</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>647794</v>
+        <v>647878</v>
       </c>
       <c r="R57" t="n">
-        <v>6943662</v>
+        <v>6944660</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7010,12 +6758,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7026,45 +6774,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323584</t>
+          <t>https://artportalen.se/Sighting/137310227</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1322963</v>
+        <v>137321970</v>
       </c>
       <c r="B58" t="n">
-        <v>93197</v>
+        <v>80132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,43 +6806,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>647228</v>
+        <v>647704</v>
       </c>
       <c r="R58" t="n">
-        <v>6943441</v>
+        <v>6944311</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7135,12 +6860,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7151,92 +6876,73 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322963</t>
+          <t>https://artportalen.se/Sighting/137321970</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1322964</v>
+        <v>137307956</v>
       </c>
       <c r="B59" t="n">
-        <v>93197</v>
+        <v>58030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>647213</v>
+        <v>647938</v>
       </c>
       <c r="R59" t="n">
-        <v>6943460</v>
+        <v>6944333</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7260,12 +6966,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7276,45 +6992,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322964</t>
+          <t>https://artportalen.se/Sighting/137307956</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1763369</v>
+        <v>137308686</v>
       </c>
       <c r="B60" t="n">
-        <v>93235</v>
+        <v>58033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7322,46 +7024,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>647228</v>
+        <v>647835</v>
       </c>
       <c r="R60" t="n">
-        <v>6943441</v>
+        <v>6944599</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7385,12 +7082,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7401,45 +7113,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763369</t>
+          <t>https://artportalen.se/Sighting/137308686</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1763370</v>
+        <v>137308687</v>
       </c>
       <c r="B61" t="n">
-        <v>93235</v>
+        <v>58033</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7447,46 +7145,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>647213</v>
+        <v>647911</v>
       </c>
       <c r="R61" t="n">
-        <v>6943460</v>
+        <v>6944464</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7510,12 +7203,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7526,34 +7234,2590 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137308687</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135039490</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>647904</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6944512</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039490</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135039491</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>1, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>647833</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6944586</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Uppskrämda.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039491</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137299948</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57220</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>647834</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6944597</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137299948</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137303210</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57220</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>647860</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6944223</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Natträd</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137303210</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137320454</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>647825</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6944444</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137320454</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135039489</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>1, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>647942</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6944520</v>
+      </c>
+      <c r="S67" t="n">
+        <v>7</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039489</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137321464</v>
+      </c>
+      <c r="B68" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>647782</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6944265</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137321464</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137320885</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58189</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>647865</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6944435</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137320885</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137320456</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>647824</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6944445</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137320456</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137302329</v>
+      </c>
+      <c r="B71" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>647885</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6944478</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137302329</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137301096</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>647887</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6944485</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137301096</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137303092</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92550</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Frölandsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>647853</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6944493</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137303092</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1763373</v>
+      </c>
+      <c r="B74" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>647086</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6943714</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
           <t>Hans Sundström</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>Hans Sundström</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
+      <c r="AY74" t="inlineStr">
         <is>
           <t>Steget Före</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763373</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1322969</v>
+      </c>
+      <c r="B75" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>647718</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6943739</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322969</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1763375</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>647646</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6943850</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763375</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>210541</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>658</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Slätberget, Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>647886</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6943600</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>svacka i hällmarkstallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/210541</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>429255</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Slätberget, Fälleberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>647886</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6943600</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>svacka i hällmarkstallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/429255</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1323584</v>
+      </c>
+      <c r="B79" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>647794</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6943662</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2011-10-24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1323584</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1322963</v>
+      </c>
+      <c r="B80" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>647228</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6943441</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322963</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1322964</v>
+      </c>
+      <c r="B81" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>647213</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1322964</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1763369</v>
+      </c>
+      <c r="B82" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>647228</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6943441</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763369</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1763370</v>
+      </c>
+      <c r="B83" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>647213</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1763370</t>
         </is>
@@ -7621,6 +9885,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ83"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1424,48 +1424,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135039486</v>
+        <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>92043</v>
+        <v>93466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>789</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647936</v>
+        <v>647834</v>
       </c>
       <c r="R9" t="n">
-        <v>6944664</v>
+        <v>6944526</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1489,22 +1500,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,30 +1524,31 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039486</t>
+          <t>https://artportalen.se/Sighting/137300680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135039492</v>
+        <v>135039486</v>
       </c>
       <c r="B10" t="n">
         <v>92043</v>
@@ -1571,13 +1583,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>647729</v>
+        <v>647936</v>
       </c>
       <c r="R10" t="n">
-        <v>6944666</v>
+        <v>6944664</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1618,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1628,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,16 +1654,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039492</t>
+          <t>https://artportalen.se/Sighting/135039486</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137302205</v>
+        <v>135039492</v>
       </c>
       <c r="B11" t="n">
-        <v>92159</v>
+        <v>92043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,17 +1691,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>647947</v>
+        <v>647729</v>
       </c>
       <c r="R11" t="n">
-        <v>6944551</v>
+        <v>6944666</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,22 +1725,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,27 +1755,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302205</t>
+          <t>https://artportalen.se/Sighting/135039492</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137300719</v>
+        <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>83381</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647928</v>
+        <v>647947</v>
       </c>
       <c r="R12" t="n">
-        <v>6944580</v>
+        <v>6944551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,16 +1878,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300719</t>
+          <t>https://artportalen.se/Sighting/137302205</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1322966</v>
+        <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>83381</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,43 +1895,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647800</v>
+        <v>647928</v>
       </c>
       <c r="R13" t="n">
-        <v>6944135</v>
+        <v>6944580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,12 +1949,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,42 +1975,28 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322966</t>
+          <t>https://artportalen.se/Sighting/137300719</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1322967</v>
+        <v>1322966</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -2027,7 +2026,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2041,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>647805</v>
+        <v>647800</v>
       </c>
       <c r="R14" t="n">
-        <v>6944182</v>
+        <v>6944135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,13 +2115,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322967</t>
+          <t>https://artportalen.se/Sighting/1322966</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1322968</v>
+        <v>1322967</v>
       </c>
       <c r="B15" t="n">
         <v>93197</v>
@@ -2152,7 +2151,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2166,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>647877</v>
+        <v>647805</v>
       </c>
       <c r="R15" t="n">
-        <v>6943956</v>
+        <v>6944182</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2219,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2241,16 +2240,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322968</t>
+          <t>https://artportalen.se/Sighting/1322967</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137300025</v>
+        <v>1322968</v>
       </c>
       <c r="B16" t="n">
-        <v>93456</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2275,17 +2274,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>647897</v>
+        <v>647877</v>
       </c>
       <c r="R16" t="n">
-        <v>6944605</v>
+        <v>6943956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,22 +2320,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,28 +2336,42 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300025</t>
+          <t>https://artportalen.se/Sighting/1322968</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137300385</v>
+        <v>137300025</v>
       </c>
       <c r="B17" t="n">
         <v>93456</v>
@@ -2394,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>647876</v>
+        <v>647897</v>
       </c>
       <c r="R17" t="n">
-        <v>6944586</v>
+        <v>6944605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,24 +2466,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Matilda Sandgren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Matilda Sandgren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300385</t>
+          <t>https://artportalen.se/Sighting/137300025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137302420</v>
+        <v>137300385</v>
       </c>
       <c r="B18" t="n">
         <v>93456</v>
@@ -2506,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>647875</v>
+        <v>647876</v>
       </c>
       <c r="R18" t="n">
-        <v>6944553</v>
+        <v>6944586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2551,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,24 +2578,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Matilda Sandgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Matilda Sandgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302420</t>
+          <t>https://artportalen.se/Sighting/137300385</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137307953</v>
+        <v>137302420</v>
       </c>
       <c r="B19" t="n">
         <v>93456</v>
@@ -2614,17 +2626,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>647873</v>
+        <v>647875</v>
       </c>
       <c r="R19" t="n">
-        <v>6944550</v>
+        <v>6944553</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,24 +2690,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307953</t>
+          <t>https://artportalen.se/Sighting/137302420</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137308684</v>
+        <v>137307953</v>
       </c>
       <c r="B20" t="n">
         <v>93456</v>
@@ -2730,13 +2742,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>647827</v>
+        <v>647873</v>
       </c>
       <c r="R20" t="n">
-        <v>6944603</v>
+        <v>6944550</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,24 +2802,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308684</t>
+          <t>https://artportalen.se/Sighting/137307953</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137310231</v>
+        <v>137308684</v>
       </c>
       <c r="B21" t="n">
         <v>93456</v>
@@ -2842,13 +2854,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>647868</v>
+        <v>647827</v>
       </c>
       <c r="R21" t="n">
-        <v>6944589</v>
+        <v>6944603</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2875,9 +2887,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,24 +2914,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310231</t>
+          <t>https://artportalen.se/Sighting/137308684</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137319904</v>
+        <v>137310231</v>
       </c>
       <c r="B22" t="n">
         <v>93456</v>
@@ -2944,13 +2966,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>647797</v>
+        <v>647868</v>
       </c>
       <c r="R22" t="n">
-        <v>6944578</v>
+        <v>6944589</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2974,12 +2996,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,13 +3027,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137319904</t>
+          <t>https://artportalen.se/Sighting/137310231</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137326956</v>
+        <v>137319904</v>
       </c>
       <c r="B23" t="n">
         <v>93456</v>
@@ -3042,14 +3064,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648123</v>
+        <v>647797</v>
       </c>
       <c r="R23" t="n">
-        <v>6944279</v>
+        <v>6944578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3107,57 +3129,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326956</t>
+          <t>https://artportalen.se/Sighting/137319904</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137308688</v>
+        <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>92143</v>
+        <v>93456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4660</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>647928</v>
+        <v>648123</v>
       </c>
       <c r="R24" t="n">
-        <v>6944362</v>
+        <v>6944279</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3181,22 +3200,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3205,49 +3214,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308688</t>
+          <t>https://artportalen.se/Sighting/137326956</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135039487</v>
+        <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92006</v>
+        <v>92143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,37 +3248,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>647939</v>
+        <v>647928</v>
       </c>
       <c r="R25" t="n">
-        <v>6944638</v>
+        <v>6944362</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3309,22 +3305,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,33 +3329,49 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039487</t>
+          <t>https://artportalen.se/Sighting/137308688</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137300276</v>
+        <v>135039487</v>
       </c>
       <c r="B26" t="n">
-        <v>92122</v>
+        <v>92006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,14 +3399,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>647918</v>
+        <v>647939</v>
       </c>
       <c r="R26" t="n">
-        <v>6944595</v>
+        <v>6944638</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3421,22 +3433,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,24 +3463,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137300276</t>
+          <t>https://artportalen.se/Sighting/135039487</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137301616</v>
+        <v>137300276</v>
       </c>
       <c r="B27" t="n">
         <v>92122</v>
@@ -3503,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>647899</v>
+        <v>647918</v>
       </c>
       <c r="R27" t="n">
-        <v>6944515</v>
+        <v>6944595</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,9 +3548,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,24 +3575,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137301616</t>
+          <t>https://artportalen.se/Sighting/137300276</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137303303</v>
+        <v>137301616</v>
       </c>
       <c r="B28" t="n">
         <v>92122</v>
@@ -3605,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>647859</v>
+        <v>647899</v>
       </c>
       <c r="R28" t="n">
-        <v>6944480</v>
+        <v>6944515</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,19 +3660,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3665,24 +3677,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303303</t>
+          <t>https://artportalen.se/Sighting/137301616</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137322516</v>
+        <v>137303303</v>
       </c>
       <c r="B29" t="n">
         <v>92122</v>
@@ -3717,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>647644</v>
+        <v>647859</v>
       </c>
       <c r="R29" t="n">
-        <v>6944201</v>
+        <v>6944480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,12 +3759,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,62 +3789,62 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137322516</t>
+          <t>https://artportalen.se/Sighting/137303303</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1763376</v>
+        <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>93235</v>
+        <v>92122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>647855</v>
+        <v>647644</v>
       </c>
       <c r="R30" t="n">
-        <v>6944106</v>
+        <v>6944201</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,12 +3871,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3869,31 +3891,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763376</t>
+          <t>https://artportalen.se/Sighting/137322516</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137299812</v>
+        <v>1763376</v>
       </c>
       <c r="B31" t="n">
-        <v>93494</v>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3918,29 +3936,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>647851</v>
+        <v>647855</v>
       </c>
       <c r="R31" t="n">
-        <v>6944635</v>
+        <v>6944106</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3964,22 +3973,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3994,24 +3993,28 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137299812</t>
+          <t>https://artportalen.se/Sighting/1763376</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137299866</v>
+        <v>137299812</v>
       </c>
       <c r="B32" t="n">
         <v>93494</v>
@@ -4039,20 +4042,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>647898</v>
+        <v>647851</v>
       </c>
       <c r="R32" t="n">
-        <v>6944618</v>
+        <v>6944635</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4081,7 +4093,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4091,7 +4103,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4106,24 +4118,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137299866</t>
+          <t>https://artportalen.se/Sighting/137299812</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137302563</v>
+        <v>137299866</v>
       </c>
       <c r="B33" t="n">
         <v>93494</v>
@@ -4158,10 +4170,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>647861</v>
+        <v>647898</v>
       </c>
       <c r="R33" t="n">
-        <v>6944549</v>
+        <v>6944618</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4193,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4203,7 +4215,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4229,13 +4241,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302563</t>
+          <t>https://artportalen.se/Sighting/137299866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137303975</v>
+        <v>137302563</v>
       </c>
       <c r="B34" t="n">
         <v>93494</v>
@@ -4266,17 +4278,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>648276</v>
+        <v>647861</v>
       </c>
       <c r="R34" t="n">
-        <v>6944192</v>
+        <v>6944549</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4305,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4315,7 +4327,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,24 +4342,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303975</t>
+          <t>https://artportalen.se/Sighting/137302563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137304833</v>
+        <v>137303975</v>
       </c>
       <c r="B35" t="n">
         <v>93494</v>
@@ -4378,17 +4390,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>648139</v>
+        <v>648276</v>
       </c>
       <c r="R35" t="n">
-        <v>6944148</v>
+        <v>6944192</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4415,9 +4427,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,24 +4454,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137304833</t>
+          <t>https://artportalen.se/Sighting/137303975</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137305557</v>
+        <v>137304833</v>
       </c>
       <c r="B36" t="n">
         <v>93494</v>
@@ -4484,10 +4506,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>648000</v>
+        <v>648139</v>
       </c>
       <c r="R36" t="n">
-        <v>6944074</v>
+        <v>6944148</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4545,13 +4567,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305557</t>
+          <t>https://artportalen.se/Sighting/137304833</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137305982</v>
+        <v>137305557</v>
       </c>
       <c r="B37" t="n">
         <v>93494</v>
@@ -4586,10 +4608,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>648060</v>
+        <v>648000</v>
       </c>
       <c r="R37" t="n">
-        <v>6944250</v>
+        <v>6944074</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4647,13 +4669,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305982</t>
+          <t>https://artportalen.se/Sighting/137305557</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137306841</v>
+        <v>137305982</v>
       </c>
       <c r="B38" t="n">
         <v>93494</v>
@@ -4688,10 +4710,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>647990</v>
+        <v>648060</v>
       </c>
       <c r="R38" t="n">
-        <v>6944630</v>
+        <v>6944250</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,13 +4771,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137306841</t>
+          <t>https://artportalen.se/Sighting/137305982</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137307957</v>
+        <v>137306841</v>
       </c>
       <c r="B39" t="n">
         <v>93494</v>
@@ -4786,17 +4808,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
         <v>647990</v>
       </c>
       <c r="R39" t="n">
-        <v>6944629</v>
+        <v>6944630</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4823,19 +4845,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4850,24 +4862,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307957</t>
+          <t>https://artportalen.se/Sighting/137306841</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137310228</v>
+        <v>137307957</v>
       </c>
       <c r="B40" t="n">
         <v>93494</v>
@@ -4902,13 +4914,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>647865</v>
+        <v>647990</v>
       </c>
       <c r="R40" t="n">
-        <v>6944615</v>
+        <v>6944629</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4935,9 +4947,19 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4952,24 +4974,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310228</t>
+          <t>https://artportalen.se/Sighting/137307957</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137310230</v>
+        <v>137310228</v>
       </c>
       <c r="B41" t="n">
         <v>93494</v>
@@ -5004,10 +5026,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>647879</v>
+        <v>647865</v>
       </c>
       <c r="R41" t="n">
-        <v>6944648</v>
+        <v>6944615</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5065,13 +5087,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310230</t>
+          <t>https://artportalen.se/Sighting/137310228</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137323297</v>
+        <v>137310230</v>
       </c>
       <c r="B42" t="n">
         <v>93494</v>
@@ -5102,17 +5124,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>647851</v>
+        <v>647879</v>
       </c>
       <c r="R42" t="n">
-        <v>6944063</v>
+        <v>6944648</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5136,12 +5158,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5167,13 +5189,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137323297</t>
+          <t>https://artportalen.se/Sighting/137310230</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137325669</v>
+        <v>137323297</v>
       </c>
       <c r="B43" t="n">
         <v>93494</v>
@@ -5208,10 +5230,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>647968</v>
+        <v>647851</v>
       </c>
       <c r="R43" t="n">
-        <v>6944329</v>
+        <v>6944063</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5269,13 +5291,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137325669</t>
+          <t>https://artportalen.se/Sighting/137323297</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137325868</v>
+        <v>137325669</v>
       </c>
       <c r="B44" t="n">
         <v>93494</v>
@@ -5310,10 +5332,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>647955</v>
+        <v>647968</v>
       </c>
       <c r="R44" t="n">
-        <v>6944342</v>
+        <v>6944329</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5371,13 +5393,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137325868</t>
+          <t>https://artportalen.se/Sighting/137325669</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137327164</v>
+        <v>137325868</v>
       </c>
       <c r="B45" t="n">
         <v>93494</v>
@@ -5412,10 +5434,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648166</v>
+        <v>647955</v>
       </c>
       <c r="R45" t="n">
-        <v>6944162</v>
+        <v>6944342</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5473,13 +5495,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327164</t>
+          <t>https://artportalen.se/Sighting/137325868</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137327225</v>
+        <v>137327164</v>
       </c>
       <c r="B46" t="n">
         <v>93494</v>
@@ -5514,10 +5536,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648189</v>
+        <v>648166</v>
       </c>
       <c r="R46" t="n">
-        <v>6944175</v>
+        <v>6944162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5575,13 +5597,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327225</t>
+          <t>https://artportalen.se/Sighting/137327164</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137327248</v>
+        <v>137327225</v>
       </c>
       <c r="B47" t="n">
         <v>93494</v>
@@ -5616,10 +5638,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648188</v>
+        <v>648189</v>
       </c>
       <c r="R47" t="n">
-        <v>6944181</v>
+        <v>6944175</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5677,13 +5699,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327248</t>
+          <t>https://artportalen.se/Sighting/137327225</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137327306</v>
+        <v>137327248</v>
       </c>
       <c r="B48" t="n">
         <v>93494</v>
@@ -5718,10 +5740,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648207</v>
+        <v>648188</v>
       </c>
       <c r="R48" t="n">
-        <v>6944170</v>
+        <v>6944181</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5779,13 +5801,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327306</t>
+          <t>https://artportalen.se/Sighting/137327248</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137327400</v>
+        <v>137327306</v>
       </c>
       <c r="B49" t="n">
         <v>93494</v>
@@ -5820,10 +5842,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648304</v>
+        <v>648207</v>
       </c>
       <c r="R49" t="n">
-        <v>6944246</v>
+        <v>6944170</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5881,13 +5903,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327400</t>
+          <t>https://artportalen.se/Sighting/137327306</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137327418</v>
+        <v>137327400</v>
       </c>
       <c r="B50" t="n">
         <v>93494</v>
@@ -5922,10 +5944,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>648306</v>
+        <v>648304</v>
       </c>
       <c r="R50" t="n">
-        <v>6944280</v>
+        <v>6944246</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5983,38 +6005,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137327418</t>
+          <t>https://artportalen.se/Sighting/137327400</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137302387</v>
+        <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>93494</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6024,10 +6046,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>647890</v>
+        <v>648306</v>
       </c>
       <c r="R51" t="n">
-        <v>6944461</v>
+        <v>6944280</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6054,12 +6076,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,13 +6107,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302387</t>
+          <t>https://artportalen.se/Sighting/137327418</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137319834</v>
+        <v>137302387</v>
       </c>
       <c r="B52" t="n">
         <v>79513</v>
@@ -6122,14 +6144,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>647807</v>
+        <v>647890</v>
       </c>
       <c r="R52" t="n">
-        <v>6944577</v>
+        <v>6944461</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6156,12 +6178,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6187,13 +6209,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137319834</t>
+          <t>https://artportalen.se/Sighting/137302387</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137326463</v>
+        <v>137319834</v>
       </c>
       <c r="B53" t="n">
         <v>79513</v>
@@ -6224,14 +6246,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>647966</v>
+        <v>647807</v>
       </c>
       <c r="R53" t="n">
-        <v>6944439</v>
+        <v>6944577</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6289,57 +6311,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137326463</t>
+          <t>https://artportalen.se/Sighting/137319834</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137307952</v>
+        <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79537</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>647859</v>
+        <v>647966</v>
       </c>
       <c r="R54" t="n">
-        <v>6944610</v>
+        <v>6944439</v>
       </c>
       <c r="S54" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6363,22 +6382,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6387,46 +6396,30 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307952</t>
+          <t>https://artportalen.se/Sighting/137326463</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137307954</v>
+        <v>137307952</v>
       </c>
       <c r="B55" t="n">
         <v>79537</v>
@@ -6464,13 +6457,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>647884</v>
+        <v>647859</v>
       </c>
       <c r="R55" t="n">
-        <v>6944388</v>
+        <v>6944610</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6499,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6551,13 +6544,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307954</t>
+          <t>https://artportalen.se/Sighting/137307952</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137308685</v>
+        <v>137307954</v>
       </c>
       <c r="B56" t="n">
         <v>79537</v>
@@ -6595,13 +6588,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>647831</v>
+        <v>647884</v>
       </c>
       <c r="R56" t="n">
-        <v>6944609</v>
+        <v>6944388</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6630,7 +6623,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6640,12 +6633,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6676,24 +6664,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308685</t>
+          <t>https://artportalen.se/Sighting/137307954</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137310227</v>
+        <v>137308685</v>
       </c>
       <c r="B57" t="n">
         <v>79537</v>
@@ -6722,19 +6710,22 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>647878</v>
+        <v>647831</v>
       </c>
       <c r="R57" t="n">
-        <v>6944660</v>
+        <v>6944609</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6761,82 +6752,113 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137310227</t>
+          <t>https://artportalen.se/Sighting/137308685</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137321970</v>
+        <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>80132</v>
+        <v>79537</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>647704</v>
+        <v>647878</v>
       </c>
       <c r="R58" t="n">
-        <v>6944311</v>
+        <v>6944660</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,12 +6882,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6891,58 +6913,54 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137321970</t>
+          <t>https://artportalen.se/Sighting/137310227</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137307956</v>
+        <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>58030</v>
+        <v>80132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>647938</v>
+        <v>647704</v>
       </c>
       <c r="R59" t="n">
-        <v>6944333</v>
+        <v>6944311</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6966,22 +6984,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6996,44 +7004,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307956</t>
+          <t>https://artportalen.se/Sighting/137321970</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137308686</v>
+        <v>137307956</v>
       </c>
       <c r="B60" t="n">
-        <v>58033</v>
+        <v>58030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7052,13 +7060,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>647835</v>
+        <v>647938</v>
       </c>
       <c r="R60" t="n">
-        <v>6944599</v>
+        <v>6944333</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7087,7 +7095,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7097,12 +7105,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7117,24 +7120,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308686</t>
+          <t>https://artportalen.se/Sighting/137307956</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137308687</v>
+        <v>137308686</v>
       </c>
       <c r="B61" t="n">
         <v>58033</v>
@@ -7173,10 +7176,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>647911</v>
+        <v>647835</v>
       </c>
       <c r="R61" t="n">
-        <v>6944464</v>
+        <v>6944599</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -7208,7 +7211,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7218,7 +7221,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7249,62 +7252,58 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308687</t>
+          <t>https://artportalen.se/Sighting/137308686</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135039490</v>
+        <v>137308687</v>
       </c>
       <c r="B62" t="n">
-        <v>57167</v>
+        <v>58033</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>647904</v>
+        <v>647911</v>
       </c>
       <c r="R62" t="n">
-        <v>6944512</v>
+        <v>6944464</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7328,22 +7327,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7358,24 +7362,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039490</t>
+          <t>https://artportalen.se/Sighting/137308687</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135039491</v>
+        <v>135039490</v>
       </c>
       <c r="B63" t="n">
         <v>57167</v>
@@ -7403,16 +7407,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>647833</v>
+        <v>647904</v>
       </c>
       <c r="R63" t="n">
-        <v>6944586</v>
+        <v>6944512</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7467,12 +7467,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Uppskrämda.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7498,16 +7493,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039491</t>
+          <t>https://artportalen.se/Sighting/135039490</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137299948</v>
+        <v>135039491</v>
       </c>
       <c r="B64" t="n">
-        <v>57220</v>
+        <v>57167</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7532,21 +7527,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>647834</v>
+        <v>647833</v>
       </c>
       <c r="R64" t="n">
-        <v>6944597</v>
+        <v>6944586</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7570,22 +7576,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Uppskrämda.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7600,24 +7611,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137299948</t>
+          <t>https://artportalen.se/Sighting/135039491</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137303210</v>
+        <v>137299948</v>
       </c>
       <c r="B65" t="n">
         <v>57220</v>
@@ -7653,10 +7664,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>647860</v>
+        <v>647834</v>
       </c>
       <c r="R65" t="n">
-        <v>6944223</v>
+        <v>6944597</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7688,7 +7699,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7698,12 +7709,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Natträd</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7729,16 +7735,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303210</t>
+          <t>https://artportalen.se/Sighting/137299948</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137320454</v>
+        <v>137303210</v>
       </c>
       <c r="B66" t="n">
-        <v>5188</v>
+        <v>57220</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7746,37 +7752,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>647825</v>
+        <v>647860</v>
       </c>
       <c r="R66" t="n">
-        <v>6944444</v>
+        <v>6944223</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7800,17 +7807,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Natträd</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7825,77 +7842,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137320454</t>
+          <t>https://artportalen.se/Sighting/137303210</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135039489</v>
+        <v>137320454</v>
       </c>
       <c r="B67" t="n">
-        <v>58141</v>
+        <v>5188</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>1, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>647942</v>
+        <v>647825</v>
       </c>
       <c r="R67" t="n">
-        <v>6944520</v>
+        <v>6944444</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7919,22 +7924,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7949,27 +7949,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135039489</t>
+          <t>https://artportalen.se/Sighting/137320454</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137321464</v>
+        <v>135039489</v>
       </c>
       <c r="B68" t="n">
-        <v>58194</v>
+        <v>58141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7996,23 +7996,30 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Frölandsberget, Ång</t>
+          <t>1, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>647782</v>
+        <v>647942</v>
       </c>
       <c r="R68" t="n">
-        <v>6944265</v>
+        <v>6944520</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8036,12 +8043,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8056,65 +8073,70 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137321464</t>
+          <t>https://artportalen.se/Sighting/135039489</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137320885</v>
+        <v>137321464</v>
       </c>
       <c r="B69" t="n">
-        <v>58189</v>
+        <v>58194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>647865</v>
+        <v>647782</v>
       </c>
       <c r="R69" t="n">
-        <v>6944435</v>
+        <v>6944265</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8169,16 +8191,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137320885</t>
+          <t>https://artportalen.se/Sighting/137321464</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137320456</v>
+        <v>137320885</v>
       </c>
       <c r="B70" t="n">
-        <v>5208</v>
+        <v>58189</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8186,16 +8208,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8210,10 +8232,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>647824</v>
+        <v>647865</v>
       </c>
       <c r="R70" t="n">
-        <v>6944445</v>
+        <v>6944435</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8248,11 +8270,6 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8276,16 +8293,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137320456</t>
+          <t>https://artportalen.se/Sighting/137320885</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137302329</v>
+        <v>137320456</v>
       </c>
       <c r="B71" t="n">
-        <v>111399</v>
+        <v>5208</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8293,21 +8310,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220240</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8317,10 +8334,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>647885</v>
+        <v>647824</v>
       </c>
       <c r="R71" t="n">
-        <v>6944478</v>
+        <v>6944445</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8347,12 +8364,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8378,38 +8400,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137302329</t>
+          <t>https://artportalen.se/Sighting/137320456</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137301096</v>
+        <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>99405</v>
+        <v>111399</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8419,10 +8441,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>647887</v>
+        <v>647885</v>
       </c>
       <c r="R72" t="n">
-        <v>6944485</v>
+        <v>6944478</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8480,38 +8502,38 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137301096</t>
+          <t>https://artportalen.se/Sighting/137302329</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137303092</v>
+        <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>92550</v>
+        <v>99405</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040162</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8521,10 +8543,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>647853</v>
+        <v>647887</v>
       </c>
       <c r="R73" t="n">
-        <v>6944493</v>
+        <v>6944485</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8554,19 +8576,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8581,27 +8593,27 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303092</t>
+          <t>https://artportalen.se/Sighting/137301096</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1763373</v>
+        <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>93235</v>
+        <v>92550</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8609,43 +8621,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5966</v>
+        <v>6040162</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>647086</v>
+        <v>647853</v>
       </c>
       <c r="R74" t="n">
-        <v>6943714</v>
+        <v>6944493</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8672,12 +8675,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8692,31 +8705,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763373</t>
+          <t>https://artportalen.se/Sighting/137303092</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1322969</v>
+        <v>1763373</v>
       </c>
       <c r="B75" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8724,26 +8733,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8753,14 +8762,14 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>647718</v>
+        <v>647086</v>
       </c>
       <c r="R75" t="n">
-        <v>6943739</v>
+        <v>6943714</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8804,16 +8813,6 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
@@ -8832,16 +8831,16 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322969</t>
+          <t>https://artportalen.se/Sighting/1763373</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1763375</v>
+        <v>1322969</v>
       </c>
       <c r="B76" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8849,26 +8848,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8882,10 +8881,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>647646</v>
+        <v>647718</v>
       </c>
       <c r="R76" t="n">
-        <v>6943850</v>
+        <v>6943739</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8929,9 +8928,14 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8952,16 +8956,16 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763375</t>
+          <t>https://artportalen.se/Sighting/1322969</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>210541</v>
+        <v>1763375</v>
       </c>
       <c r="B77" t="n">
-        <v>92208</v>
+        <v>93235</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8969,46 +8973,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Slätberget, Fälleberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>647886</v>
+        <v>647646</v>
       </c>
       <c r="R77" t="n">
-        <v>6943600</v>
+        <v>6943850</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9032,12 +9036,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2013-05-11</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9051,38 +9055,37 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>svacka i hällmarkstallnaturskog</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/210541</t>
+          <t>https://artportalen.se/Sighting/1763375</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>429255</v>
+        <v>210541</v>
       </c>
       <c r="B78" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9090,21 +9093,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9194,16 +9197,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/429255</t>
+          <t>https://artportalen.se/Sighting/210541</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1323584</v>
+        <v>429255</v>
       </c>
       <c r="B79" t="n">
-        <v>93197</v>
+        <v>91909</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9211,46 +9214,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Slätberget, Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>647794</v>
+        <v>647886</v>
       </c>
       <c r="R79" t="n">
-        <v>6943662</v>
+        <v>6943600</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9274,12 +9277,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2013-05-11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2013-05-11</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9291,41 +9294,37 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>svacka i hällmarkstallnaturskog</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323584</t>
+          <t>https://artportalen.se/Sighting/429255</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1322963</v>
+        <v>1323584</v>
       </c>
       <c r="B80" t="n">
         <v>93197</v>
@@ -9355,7 +9354,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9365,14 +9364,14 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>647228</v>
+        <v>647794</v>
       </c>
       <c r="R80" t="n">
-        <v>6943441</v>
+        <v>6943662</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9399,12 +9398,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9444,13 +9443,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322963</t>
+          <t>https://artportalen.se/Sighting/1323584</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1322964</v>
+        <v>1322963</v>
       </c>
       <c r="B81" t="n">
         <v>93197</v>
@@ -9480,7 +9479,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9494,10 +9493,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>647213</v>
+        <v>647228</v>
       </c>
       <c r="R81" t="n">
-        <v>6943460</v>
+        <v>6943441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9569,16 +9568,16 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322964</t>
+          <t>https://artportalen.se/Sighting/1322963</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1763369</v>
+        <v>1322964</v>
       </c>
       <c r="B82" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9586,26 +9585,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9619,10 +9618,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>647228</v>
+        <v>647213</v>
       </c>
       <c r="R82" t="n">
-        <v>6943441</v>
+        <v>6943460</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9694,13 +9693,13 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763369</t>
+          <t>https://artportalen.se/Sighting/1322964</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1763370</v>
+        <v>1763369</v>
       </c>
       <c r="B83" t="n">
         <v>93235</v>
@@ -9730,7 +9729,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9744,10 +9743,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>647213</v>
+        <v>647228</v>
       </c>
       <c r="R83" t="n">
-        <v>6943460</v>
+        <v>6943441</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9818,6 +9817,131 @@
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763369</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1763370</v>
+      </c>
+      <c r="B84" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>647213</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6943460</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1763370</t>
         </is>
@@ -9907,6 +10031,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93466</v>
+        <v>93471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92143</v>
+        <v>92146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>137302387</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>137319834</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>137307952</v>
       </c>
       <c r="B55" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>137307954</v>
       </c>
       <c r="B56" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137308685</v>
       </c>
       <c r="B57" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>137307956</v>
       </c>
       <c r="B60" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>137308686</v>
       </c>
       <c r="B61" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137308687</v>
       </c>
       <c r="B62" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>137299948</v>
       </c>
       <c r="B65" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>137303210</v>
       </c>
       <c r="B66" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>137321464</v>
       </c>
       <c r="B69" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137320885</v>
       </c>
       <c r="B70" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93471</v>
+        <v>93473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92146</v>
+        <v>92148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93473</v>
+        <v>93479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>137302387</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>137319834</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>137307952</v>
       </c>
       <c r="B55" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>137307954</v>
       </c>
       <c r="B56" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137308685</v>
       </c>
       <c r="B57" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>137307956</v>
       </c>
       <c r="B60" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>137308686</v>
       </c>
       <c r="B61" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137308687</v>
       </c>
       <c r="B62" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>137321464</v>
       </c>
       <c r="B69" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137320885</v>
       </c>
       <c r="B70" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93479</v>
+        <v>93491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92153</v>
+        <v>92165</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>137302387</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>137319834</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>137307952</v>
       </c>
       <c r="B55" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>137307954</v>
       </c>
       <c r="B56" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137308685</v>
       </c>
       <c r="B57" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92560</v>
+        <v>92572</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92165</v>
+        <v>92166</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>137302387</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>137319834</v>
       </c>
       <c r="B53" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>137307952</v>
       </c>
       <c r="B55" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>137307954</v>
       </c>
       <c r="B56" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137308685</v>
       </c>
       <c r="B57" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92572</v>
+        <v>92573</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93492</v>
+        <v>93495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>137302387</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>137319834</v>
       </c>
       <c r="B53" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>137307952</v>
       </c>
       <c r="B55" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>137307954</v>
       </c>
       <c r="B56" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137308685</v>
       </c>
       <c r="B57" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 5881-2024 artfynd.xlsx
+++ b/artfynd/A 5881-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137306302</v>
       </c>
       <c r="B4" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>137306578</v>
       </c>
       <c r="B5" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>137324302</v>
       </c>
       <c r="B6" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137324637</v>
       </c>
       <c r="B7" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>137325198</v>
       </c>
       <c r="B8" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>137300680</v>
       </c>
       <c r="B9" t="n">
-        <v>93495</v>
+        <v>93499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>137302205</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137300719</v>
       </c>
       <c r="B13" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>137300025</v>
       </c>
       <c r="B17" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>137300385</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137302420</v>
       </c>
       <c r="B19" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>137307953</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>137308684</v>
       </c>
       <c r="B21" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>137310231</v>
       </c>
       <c r="B22" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>137319904</v>
       </c>
       <c r="B23" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>137326956</v>
       </c>
       <c r="B24" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137308688</v>
       </c>
       <c r="B25" t="n">
-        <v>92169</v>
+        <v>92173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137300276</v>
       </c>
       <c r="B27" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137301616</v>
       </c>
       <c r="B28" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>137303303</v>
       </c>
       <c r="B29" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>137322516</v>
       </c>
       <c r="B30" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>137299812</v>
       </c>
       <c r="B32" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>137299866</v>
       </c>
       <c r="B33" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>137302563</v>
       </c>
       <c r="B34" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>137303975</v>
       </c>
       <c r="B35" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>137304833</v>
       </c>
       <c r="B36" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>137305557</v>
       </c>
       <c r="B37" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>137305982</v>
       </c>
       <c r="B38" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137306841</v>
       </c>
       <c r="B39" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>137307957</v>
       </c>
       <c r="B40" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>137310228</v>
       </c>
       <c r="B41" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>137310230</v>
       </c>
       <c r="B42" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>137323297</v>
       </c>
       <c r="B43" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>137325669</v>
       </c>
       <c r="B44" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>137325868</v>
       </c>
       <c r="B45" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>137327164</v>
       </c>
       <c r="B46" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>137327225</v>
       </c>
       <c r="B47" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137327248</v>
       </c>
       <c r="B48" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>137327306</v>
       </c>
       <c r="B49" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>137327400</v>
       </c>
       <c r="B50" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137327418</v>
       </c>
       <c r="B51" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>137302387</v>
       </c>
       <c r="B52" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>137319834</v>
       </c>
       <c r="B53" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>137326463</v>
       </c>
       <c r="B54" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>137307952</v>
       </c>
       <c r="B55" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>137307954</v>
       </c>
       <c r="B56" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137308685</v>
       </c>
       <c r="B57" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>137310227</v>
       </c>
       <c r="B58" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137321970</v>
       </c>
       <c r="B59" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>137307956</v>
       </c>
       <c r="B60" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>137308686</v>
       </c>
       <c r="B61" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137308687</v>
       </c>
       <c r="B62" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>137299948</v>
       </c>
       <c r="B65" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>137303210</v>
       </c>
       <c r="B66" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>137321464</v>
       </c>
       <c r="B69" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>137320885</v>
       </c>
       <c r="B70" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>137302329</v>
       </c>
       <c r="B72" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>137301096</v>
       </c>
       <c r="B73" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>137303092</v>
       </c>
       <c r="B74" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
